--- a/output/pdf_financials_xlsx/TTS.xlsx
+++ b/output/pdf_financials_xlsx/TTS.xlsx
@@ -1044,13 +1044,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.25515</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.5140980000000001</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.276269</v>
       </c>
     </row>
     <row r="13">
@@ -1983,13 +1983,13 @@
         <v>9.132845</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>9.132845</v>
+        <v>9.387995</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.614437</v>
+        <v>-2.100339</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>5.792942</v>
+        <v>6.069211</v>
       </c>
     </row>
     <row r="28">
@@ -2093,13 +2093,13 @@
         <v>9.132845</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>9.132845</v>
+        <v>9.387995</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.614437</v>
+        <v>-2.100339</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>5.792942</v>
+        <v>6.069211</v>
       </c>
     </row>
     <row r="30">
@@ -2366,7 +2366,7 @@
         <v>0.090998</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.210411</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>9.560459</v>
@@ -2476,7 +2476,7 @@
         <v>0.090998</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.210411</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>9.560459</v>
@@ -3136,7 +3136,7 @@
         <v>0.864333</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.225964</v>
+        <v>0.015553</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.016153</v>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -24852,7 +24852,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">

--- a/output/pdf_financials_xlsx/TTS.xlsx
+++ b/output/pdf_financials_xlsx/TTS.xlsx
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.056515</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -23326,7 +23326,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -23614,7 +23618,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>0.009174</v>
       </c>
